--- a/data/models/anthropic.xlsx
+++ b/data/models/anthropic.xlsx
@@ -29,7 +29,7 @@
     <t xml:space="preserve">Anthropic (private)</t>
   </si>
   <si>
-    <t xml:space="preserve">Scenario model: 2030 earning power, capitalised and discounted back four years  ·  Inputs in blue can be changed; everything else recalculates.</t>
+    <t xml:space="preserve">Scenario model: 2030 earning power, capitalised and discounted back four years, plus cash flow along the way  ·  Inputs in blue can be changed; everything else recalculates.</t>
   </si>
   <si>
     <t xml:space="preserve">SCENARIOS</t>
@@ -817,7 +817,7 @@
         <v>0.13</v>
       </c>
       <c r="C16" s="18" t="n">
-        <f aca="false">(Model!$C$19/(1+B16)^Model!$C$13+Model!$C$14)</f>
+        <f aca="false">(Model!$C$19/(1+B16)^Model!$C$13+0+Model!$C$14)</f>
         <v>908.478365375077</v>
       </c>
     </row>
@@ -827,7 +827,7 @@
         <v>0.14</v>
       </c>
       <c r="C17" s="18" t="n">
-        <f aca="false">(Model!$C$19/(1+B17)^Model!$C$13+Model!$C$14)</f>
+        <f aca="false">(Model!$C$19/(1+B17)^Model!$C$13+0+Model!$C$14)</f>
         <v>877.018910854593</v>
       </c>
     </row>
@@ -837,7 +837,7 @@
         <v>0.15</v>
       </c>
       <c r="C18" s="18" t="n">
-        <f aca="false">(Model!$C$19/(1+B18)^Model!$C$13+Model!$C$14)</f>
+        <f aca="false">(Model!$C$19/(1+B18)^Model!$C$13+0+Model!$C$14)</f>
         <v>846.909495034681</v>
       </c>
     </row>
@@ -847,7 +847,7 @@
         <v>0.16</v>
       </c>
       <c r="C19" s="18" t="n">
-        <f aca="false">(Model!$C$19/(1+B19)^Model!$C$13+Model!$C$14)</f>
+        <f aca="false">(Model!$C$19/(1+B19)^Model!$C$13+0+Model!$C$14)</f>
         <v>818.081188735453</v>
       </c>
     </row>
@@ -857,7 +857,7 @@
         <v>0.17</v>
       </c>
       <c r="C20" s="18" t="n">
-        <f aca="false">(Model!$C$19/(1+B20)^Model!$C$13+Model!$C$14)</f>
+        <f aca="false">(Model!$C$19/(1+B20)^Model!$C$13+0+Model!$C$14)</f>
         <v>790.469133945367</v>
       </c>
     </row>
